--- a/NPV_calculations_5.2.xlsx
+++ b/NPV_calculations_5.2.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10215"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10222"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/benjaros/Documents/GitHub/wealth_tax/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ben/Documents/GitHub/wealth_tax/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7379905D-E4CD-9849-9C5C-E87CBBD5F935}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A1CD616-FA7D-9E45-8B9A-83B85A5CAC2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1500" yWindow="1400" windowWidth="27640" windowHeight="16680" xr2:uid="{DF18EB8C-62AB-9F48-A3D3-B2EAD614B548}"/>
+    <workbookView xWindow="1160" yWindow="1320" windowWidth="27640" windowHeight="16680" xr2:uid="{DF18EB8C-62AB-9F48-A3D3-B2EAD614B548}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029" iterateDelta="1E-4"/>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -774,7 +774,7 @@
         <v>15</v>
       </c>
       <c r="B27" s="8">
-        <v>0.03</v>
+        <v>1.4999999999999999E-2</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.2">
@@ -782,7 +782,7 @@
         <v>16</v>
       </c>
       <c r="B28" s="8">
-        <v>0.05</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.2">
@@ -790,7 +790,7 @@
         <v>17</v>
       </c>
       <c r="B29" s="8">
-        <v>7.0000000000000007E-2</v>
+        <v>4.4999999999999998E-2</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.2">
@@ -831,7 +831,7 @@
     <row r="35" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A35" s="7">
         <f>B27</f>
-        <v>0.03</v>
+        <v>1.4999999999999999E-2</v>
       </c>
       <c r="B35" s="5">
         <f>B14*B13</f>
@@ -839,17 +839,17 @@
       </c>
       <c r="C35" s="11">
         <f>B14*B13/B27</f>
-        <v>98.36322869955157</v>
+        <v>196.72645739910314</v>
       </c>
       <c r="D35" s="12">
         <f>B12-C35</f>
-        <v>-50.36322869955157</v>
+        <v>-148.72645739910314</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A36" s="7">
         <f>B28</f>
-        <v>0.05</v>
+        <v>0.03</v>
       </c>
       <c r="B36" s="5">
         <f>B14*B13</f>
@@ -857,17 +857,17 @@
       </c>
       <c r="C36" s="11">
         <f>B14*B13/B28</f>
-        <v>59.017937219730939</v>
+        <v>98.36322869955157</v>
       </c>
       <c r="D36" s="12">
         <f>B12-C36</f>
-        <v>-11.017937219730939</v>
+        <v>-50.36322869955157</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A37" s="7">
         <f>B29</f>
-        <v>7.0000000000000007E-2</v>
+        <v>4.4999999999999998E-2</v>
       </c>
       <c r="B37" s="5">
         <f>B14*B13</f>
@@ -875,11 +875,11 @@
       </c>
       <c r="C37" s="11">
         <f>B14*B13/B29</f>
-        <v>42.155669442664959</v>
+        <v>65.575485799701056</v>
       </c>
       <c r="D37" s="12">
         <f>B12-C37</f>
-        <v>5.8443305573350415</v>
+        <v>-17.575485799701056</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.2">
@@ -904,7 +904,7 @@
     <row r="41" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A41" s="7">
         <f>B27</f>
-        <v>0.03</v>
+        <v>1.4999999999999999E-2</v>
       </c>
       <c r="B41" s="5">
         <f>B19*B18</f>
@@ -912,17 +912,17 @@
       </c>
       <c r="C41" s="11">
         <f>B19*B18/B27</f>
-        <v>62.531763826606884</v>
+        <v>125.06352765321377</v>
       </c>
       <c r="D41" s="12">
         <f>B17-C41</f>
-        <v>3.5282361733931182</v>
+        <v>-59.003527653213766</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A42" s="7">
         <f>B28</f>
-        <v>0.05</v>
+        <v>0.03</v>
       </c>
       <c r="B42" s="5">
         <f>B19*B18</f>
@@ -930,17 +930,17 @@
       </c>
       <c r="C42" s="11">
         <f>B19*B18/B28</f>
-        <v>37.519058295964122</v>
+        <v>62.531763826606884</v>
       </c>
       <c r="D42" s="12">
         <f>B17-C42</f>
-        <v>28.54094170403588</v>
+        <v>3.5282361733931182</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A43" s="7">
         <f>B29</f>
-        <v>7.0000000000000007E-2</v>
+        <v>4.4999999999999998E-2</v>
       </c>
       <c r="B43" s="5">
         <f>B19*B18</f>
@@ -948,11 +948,11 @@
       </c>
       <c r="C43" s="11">
         <f>B19*B18/B29</f>
-        <v>26.79932735426009</v>
+        <v>41.687842551071256</v>
       </c>
       <c r="D43" s="12">
         <f>B17-C43</f>
-        <v>39.260672645739916</v>
+        <v>24.372157448928746</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.2">
@@ -977,7 +977,7 @@
     <row r="48" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A48" s="7">
         <f>B27</f>
-        <v>0.03</v>
+        <v>1.4999999999999999E-2</v>
       </c>
       <c r="B48" s="5">
         <f>B24*B23</f>
@@ -985,17 +985,17 @@
       </c>
       <c r="C48" s="11">
         <f>B24*B23/B27</f>
-        <v>113.86148480318883</v>
+        <v>227.72296960637766</v>
       </c>
       <c r="D48" s="12">
         <f>B22-C48</f>
-        <v>-69.86148480318883</v>
+        <v>-183.72296960637766</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A49" s="7">
         <f>B28</f>
-        <v>0.05</v>
+        <v>0.03</v>
       </c>
       <c r="B49" s="5">
         <f>B24*B23</f>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C49" s="11">
         <f>B24*B23/B28</f>
-        <v>68.316890881913295</v>
+        <v>113.86148480318883</v>
       </c>
       <c r="D49" s="12">
         <f>B22-C49</f>
-        <v>-24.316890881913295</v>
+        <v>-69.86148480318883</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A50" s="7">
         <f>B29</f>
-        <v>7.0000000000000007E-2</v>
+        <v>4.4999999999999998E-2</v>
       </c>
       <c r="B50" s="5">
         <f>B24*B23</f>
@@ -1021,11 +1021,11 @@
       </c>
       <c r="C50" s="11">
         <f>B24*B23/B29</f>
-        <v>48.797779201366637</v>
+        <v>75.907656535459225</v>
       </c>
       <c r="D50" s="12">
         <f>B22-C50</f>
-        <v>-4.7977792013666374</v>
+        <v>-31.907656535459225</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.2">
@@ -1058,15 +1058,15 @@
       </c>
       <c r="B56" s="7">
         <f>B27</f>
-        <v>0.03</v>
+        <v>1.4999999999999999E-2</v>
       </c>
       <c r="C56" s="7">
         <f>(B12*B27)/B13</f>
-        <v>0.2691588785046729</v>
+        <v>0.13457943925233645</v>
       </c>
       <c r="D56" s="13">
         <f t="shared" ref="D56:D64" si="0">C56*214</f>
-        <v>57.6</v>
+        <v>28.8</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.2">
@@ -1075,15 +1075,15 @@
       </c>
       <c r="B57" s="15">
         <f>B28</f>
-        <v>0.05</v>
+        <v>0.03</v>
       </c>
       <c r="C57" s="15">
         <f>(B12*B28)/B13</f>
-        <v>0.4485981308411216</v>
+        <v>0.2691588785046729</v>
       </c>
       <c r="D57" s="16">
         <f t="shared" si="0"/>
-        <v>96.000000000000028</v>
+        <v>57.6</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.2">
@@ -1092,15 +1092,15 @@
       </c>
       <c r="B58" s="7">
         <f>B29</f>
-        <v>7.0000000000000007E-2</v>
+        <v>4.4999999999999998E-2</v>
       </c>
       <c r="C58" s="7">
         <f>(B12*B29)/B13</f>
-        <v>0.62803738317757019</v>
+        <v>0.40373831775700941</v>
       </c>
       <c r="D58" s="13">
         <f t="shared" si="0"/>
-        <v>134.4</v>
+        <v>86.40000000000002</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.2">
@@ -1109,15 +1109,15 @@
       </c>
       <c r="B59" s="15">
         <f>B27</f>
-        <v>0.03</v>
+        <v>1.4999999999999999E-2</v>
       </c>
       <c r="C59" s="15">
         <f>(B17*B27)/B18</f>
-        <v>0.40444897959183673</v>
+        <v>0.20222448979591837</v>
       </c>
       <c r="D59" s="16">
         <f t="shared" si="0"/>
-        <v>86.552081632653056</v>
+        <v>43.276040816326528</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.2">
@@ -1126,15 +1126,15 @@
       </c>
       <c r="B60" s="7">
         <f>B28</f>
-        <v>0.05</v>
+        <v>0.03</v>
       </c>
       <c r="C60" s="7">
         <f>(B17*B28)/B18</f>
-        <v>0.6740816326530612</v>
+        <v>0.40444897959183673</v>
       </c>
       <c r="D60" s="13">
         <f t="shared" si="0"/>
-        <v>144.2534693877551</v>
+        <v>86.552081632653056</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.2">
@@ -1143,15 +1143,15 @@
       </c>
       <c r="B61" s="15">
         <f>B29</f>
-        <v>7.0000000000000007E-2</v>
+        <v>4.4999999999999998E-2</v>
       </c>
       <c r="C61" s="15">
         <f>(B17*B29)/B18</f>
-        <v>0.94371428571428584</v>
+        <v>0.60667346938775513</v>
       </c>
       <c r="D61" s="16">
         <f t="shared" si="0"/>
-        <v>201.95485714285718</v>
+        <v>129.8281224489796</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.2">
@@ -1160,15 +1160,15 @@
       </c>
       <c r="B62" s="7">
         <f>B27</f>
-        <v>0.03</v>
+        <v>1.4999999999999999E-2</v>
       </c>
       <c r="C62" s="7">
         <f>(B22*B27)/B23</f>
-        <v>0.22758620689655171</v>
+        <v>0.11379310344827585</v>
       </c>
       <c r="D62" s="13">
         <f t="shared" si="0"/>
-        <v>48.703448275862065</v>
+        <v>24.351724137931033</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.2">
@@ -1177,15 +1177,15 @@
       </c>
       <c r="B63" s="15">
         <f>B28</f>
-        <v>0.05</v>
+        <v>0.03</v>
       </c>
       <c r="C63" s="15">
         <f>(B22*B28)/B23</f>
-        <v>0.37931034482758624</v>
+        <v>0.22758620689655171</v>
       </c>
       <c r="D63" s="16">
         <f t="shared" si="0"/>
-        <v>81.172413793103459</v>
+        <v>48.703448275862065</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.2">
@@ -1194,15 +1194,15 @@
       </c>
       <c r="B64" s="7">
         <f>B29</f>
-        <v>7.0000000000000007E-2</v>
+        <v>4.4999999999999998E-2</v>
       </c>
       <c r="C64" s="7">
         <f>(B22*B29)/B23</f>
-        <v>0.53103448275862075</v>
+        <v>0.3413793103448276</v>
       </c>
       <c r="D64" s="13">
         <f t="shared" si="0"/>
-        <v>113.64137931034485</v>
+        <v>73.055172413793102</v>
       </c>
     </row>
   </sheetData>

--- a/NPV_calculations_5.2.xlsx
+++ b/NPV_calculations_5.2.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10222"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10215"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ben/Documents/GitHub/wealth_tax/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/benjaros/Documents/GitHub/wealth_tax/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A1CD616-FA7D-9E45-8B9A-83B85A5CAC2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82017F4C-FB84-F44D-A067-69013520DEAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1160" yWindow="1320" windowWidth="27640" windowHeight="16680" xr2:uid="{DF18EB8C-62AB-9F48-A3D3-B2EAD614B548}"/>
   </bookViews>
@@ -626,7 +626,7 @@
         <v>2</v>
       </c>
       <c r="B5" s="4">
-        <v>107.04</v>
+        <v>94.2</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>3</v>
@@ -648,7 +648,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="4">
-        <v>4.9000000000000004</v>
+        <v>3.3</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>3</v>
@@ -660,7 +660,7 @@
       </c>
       <c r="B8" s="5">
         <f>AVERAGE(B6,B7)</f>
-        <v>5.35</v>
+        <v>4.55</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>3</v>
@@ -681,7 +681,7 @@
         <v>9</v>
       </c>
       <c r="B12" s="4">
-        <v>48</v>
+        <v>42</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
@@ -689,8 +689,7 @@
         <v>10</v>
       </c>
       <c r="B13" s="5">
-        <f>B8</f>
-        <v>5.35</v>
+        <v>4.55</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.2">
@@ -699,7 +698,7 @@
       </c>
       <c r="B14" s="7">
         <f>1-(B12/B5)</f>
-        <v>0.55156950672645744</v>
+        <v>0.55414012738853502</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.2">
@@ -712,7 +711,7 @@
         <v>9</v>
       </c>
       <c r="B17" s="4">
-        <v>66.06</v>
+        <v>67.510000000000005</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.2">
@@ -721,7 +720,7 @@
       </c>
       <c r="B18" s="5">
         <f>B7</f>
-        <v>4.9000000000000004</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.2">
@@ -730,7 +729,7 @@
       </c>
       <c r="B19" s="7">
         <f>1-(B17/B5)</f>
-        <v>0.38284753363228696</v>
+        <v>0.28333333333333333</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.2">
@@ -743,7 +742,7 @@
         <v>9</v>
       </c>
       <c r="B22" s="4">
-        <v>44</v>
+        <v>35</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.2">
@@ -761,7 +760,7 @@
       </c>
       <c r="B24" s="7">
         <f>1-(B22/B5)</f>
-        <v>0.58893871449925261</v>
+        <v>0.62845010615711261</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.2">
@@ -804,14 +803,14 @@
       </c>
       <c r="B33" s="9">
         <f>B12</f>
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>20</v>
       </c>
       <c r="D33" s="9">
         <f>B13</f>
-        <v>5.35</v>
+        <v>4.55</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.2">
@@ -835,15 +834,15 @@
       </c>
       <c r="B35" s="5">
         <f>B14*B13</f>
-        <v>2.9508968609865471</v>
+        <v>2.5213375796178341</v>
       </c>
       <c r="C35" s="11">
         <f>B14*B13/B27</f>
-        <v>196.72645739910314</v>
+        <v>168.08917197452229</v>
       </c>
       <c r="D35" s="12">
         <f>B12-C35</f>
-        <v>-148.72645739910314</v>
+        <v>-126.08917197452229</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.2">
@@ -853,15 +852,15 @@
       </c>
       <c r="B36" s="5">
         <f>B14*B13</f>
-        <v>2.9508968609865471</v>
+        <v>2.5213375796178341</v>
       </c>
       <c r="C36" s="11">
         <f>B14*B13/B28</f>
-        <v>98.36322869955157</v>
+        <v>84.044585987261144</v>
       </c>
       <c r="D36" s="12">
         <f>B12-C36</f>
-        <v>-50.36322869955157</v>
+        <v>-42.044585987261144</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.2">
@@ -871,15 +870,15 @@
       </c>
       <c r="B37" s="5">
         <f>B14*B13</f>
-        <v>2.9508968609865471</v>
+        <v>2.5213375796178341</v>
       </c>
       <c r="C37" s="11">
         <f>B14*B13/B29</f>
-        <v>65.575485799701056</v>
+        <v>56.029723991507424</v>
       </c>
       <c r="D37" s="12">
         <f>B12-C37</f>
-        <v>-17.575485799701056</v>
+        <v>-14.029723991507424</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.2">
@@ -908,15 +907,15 @@
       </c>
       <c r="B41" s="5">
         <f>B19*B18</f>
-        <v>1.8759529147982064</v>
+        <v>0.93499999999999994</v>
       </c>
       <c r="C41" s="11">
         <f>B19*B18/B27</f>
-        <v>125.06352765321377</v>
+        <v>62.333333333333329</v>
       </c>
       <c r="D41" s="12">
         <f>B17-C41</f>
-        <v>-59.003527653213766</v>
+        <v>5.1766666666666765</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.2">
@@ -926,15 +925,15 @@
       </c>
       <c r="B42" s="5">
         <f>B19*B18</f>
-        <v>1.8759529147982064</v>
+        <v>0.93499999999999994</v>
       </c>
       <c r="C42" s="11">
         <f>B19*B18/B28</f>
-        <v>62.531763826606884</v>
+        <v>31.166666666666664</v>
       </c>
       <c r="D42" s="12">
         <f>B17-C42</f>
-        <v>3.5282361733931182</v>
+        <v>36.343333333333341</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.2">
@@ -944,15 +943,15 @@
       </c>
       <c r="B43" s="5">
         <f>B19*B18</f>
-        <v>1.8759529147982064</v>
+        <v>0.93499999999999994</v>
       </c>
       <c r="C43" s="11">
         <f>B19*B18/B29</f>
-        <v>41.687842551071256</v>
+        <v>20.777777777777779</v>
       </c>
       <c r="D43" s="12">
         <f>B17-C43</f>
-        <v>24.372157448928746</v>
+        <v>46.732222222222227</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.2">
@@ -981,15 +980,15 @@
       </c>
       <c r="B48" s="5">
         <f>B24*B23</f>
-        <v>3.4158445440956648</v>
+        <v>3.6450106157112532</v>
       </c>
       <c r="C48" s="11">
         <f>B24*B23/B27</f>
-        <v>227.72296960637766</v>
+        <v>243.00070771408355</v>
       </c>
       <c r="D48" s="12">
         <f>B22-C48</f>
-        <v>-183.72296960637766</v>
+        <v>-208.00070771408355</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.2">
@@ -999,15 +998,15 @@
       </c>
       <c r="B49" s="5">
         <f>B24*B23</f>
-        <v>3.4158445440956648</v>
+        <v>3.6450106157112532</v>
       </c>
       <c r="C49" s="11">
         <f>B24*B23/B28</f>
-        <v>113.86148480318883</v>
+        <v>121.50035385704177</v>
       </c>
       <c r="D49" s="12">
         <f>B22-C49</f>
-        <v>-69.86148480318883</v>
+        <v>-86.500353857041773</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.2">
@@ -1017,15 +1016,15 @@
       </c>
       <c r="B50" s="5">
         <f>B24*B23</f>
-        <v>3.4158445440956648</v>
+        <v>3.6450106157112532</v>
       </c>
       <c r="C50" s="11">
         <f>B24*B23/B29</f>
-        <v>75.907656535459225</v>
+        <v>81.00023590469452</v>
       </c>
       <c r="D50" s="12">
         <f>B22-C50</f>
-        <v>-31.907656535459225</v>
+        <v>-46.00023590469452</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.2">
@@ -1062,11 +1061,11 @@
       </c>
       <c r="C56" s="7">
         <f>(B12*B27)/B13</f>
-        <v>0.13457943925233645</v>
+        <v>0.13846153846153847</v>
       </c>
       <c r="D56" s="13">
         <f t="shared" ref="D56:D64" si="0">C56*214</f>
-        <v>28.8</v>
+        <v>29.630769230769232</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.2">
@@ -1079,11 +1078,11 @@
       </c>
       <c r="C57" s="15">
         <f>(B12*B28)/B13</f>
-        <v>0.2691588785046729</v>
+        <v>0.27692307692307694</v>
       </c>
       <c r="D57" s="16">
         <f t="shared" si="0"/>
-        <v>57.6</v>
+        <v>59.261538461538464</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.2">
@@ -1096,11 +1095,11 @@
       </c>
       <c r="C58" s="7">
         <f>(B12*B29)/B13</f>
-        <v>0.40373831775700941</v>
+        <v>0.41538461538461535</v>
       </c>
       <c r="D58" s="13">
         <f t="shared" si="0"/>
-        <v>86.40000000000002</v>
+        <v>88.892307692307682</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.2">
@@ -1113,11 +1112,11 @@
       </c>
       <c r="C59" s="15">
         <f>(B17*B27)/B18</f>
-        <v>0.20222448979591837</v>
+        <v>0.30686363636363639</v>
       </c>
       <c r="D59" s="16">
         <f t="shared" si="0"/>
-        <v>43.276040816326528</v>
+        <v>65.668818181818182</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.2">
@@ -1130,11 +1129,11 @@
       </c>
       <c r="C60" s="7">
         <f>(B17*B28)/B18</f>
-        <v>0.40444897959183673</v>
+        <v>0.61372727272727279</v>
       </c>
       <c r="D60" s="13">
         <f t="shared" si="0"/>
-        <v>86.552081632653056</v>
+        <v>131.33763636363636</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.2">
@@ -1147,11 +1146,11 @@
       </c>
       <c r="C61" s="15">
         <f>(B17*B29)/B18</f>
-        <v>0.60667346938775513</v>
+        <v>0.92059090909090913</v>
       </c>
       <c r="D61" s="16">
         <f t="shared" si="0"/>
-        <v>129.8281224489796</v>
+        <v>197.00645454545455</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.2">
@@ -1164,11 +1163,11 @@
       </c>
       <c r="C62" s="7">
         <f>(B22*B27)/B23</f>
-        <v>0.11379310344827585</v>
+        <v>9.0517241379310345E-2</v>
       </c>
       <c r="D62" s="13">
         <f t="shared" si="0"/>
-        <v>24.351724137931033</v>
+        <v>19.370689655172413</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.2">
@@ -1181,11 +1180,11 @@
       </c>
       <c r="C63" s="15">
         <f>(B22*B28)/B23</f>
-        <v>0.22758620689655171</v>
+        <v>0.18103448275862069</v>
       </c>
       <c r="D63" s="16">
         <f t="shared" si="0"/>
-        <v>48.703448275862065</v>
+        <v>38.741379310344826</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.2">
@@ -1198,11 +1197,11 @@
       </c>
       <c r="C64" s="7">
         <f>(B22*B29)/B23</f>
-        <v>0.3413793103448276</v>
+        <v>0.27155172413793105</v>
       </c>
       <c r="D64" s="13">
         <f t="shared" si="0"/>
-        <v>73.055172413793102</v>
+        <v>58.112068965517246</v>
       </c>
     </row>
   </sheetData>
